--- a/companies/alder-ridge/source-files/Shared/Finance/Treasury/Bank - covenants/FY27 covenant forecast - WORKING.xlsx
+++ b/companies/alder-ridge/source-files/Shared/Finance/Treasury/Bank - covenants/FY27 covenant forecast - WORKING.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast Inputs" sheetId="1" r:id="R0a64ebf6b5c14cb6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="2" r:id="Rbe70ad39e6d24f67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covenant Forecast" sheetId="3" r:id="R177ece3ac858440d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Downside" sheetId="4" r:id="Re40d85d4025b422c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="5" r:id="R5ea44deb7d2c403b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast Inputs" sheetId="1" r:id="Rb419116265204649"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="2" r:id="R4babc73c4be249e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covenant Forecast" sheetId="3" r:id="R9ff1fcc6bc114be8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Downside" sheetId="4" r:id="R9cef0839a2d34a60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="5" r:id="R845b00f7c64142a4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -256,7 +256,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Alder Ridge Finance" id="{9ACB837F-539F-4ABA-AF7F-4432F0A5EF44}"/>
+  <xltc:person displayName="Alder Ridge Finance" id="{985C9149-0327-48D7-8FF3-3DEAF244E7DB}"/>
 </xltc:personList>
 </file>
 
@@ -624,7 +624,7 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F7" s="23" t="str">
-        <x:v>Capital expenditures</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="G7" s="26" t="n">
         <x:v>620000</x:v>
@@ -828,7 +828,7 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F13" s="23" t="str">
-        <x:v>Capital expenditures</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="G13" s="26" t="n">
         <x:v>620000</x:v>
@@ -1032,7 +1032,7 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F19" s="23" t="str">
-        <x:v>Capital expenditures</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="G19" s="26" t="n">
         <x:v>620000</x:v>
@@ -1236,7 +1236,7 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F25" s="23" t="str">
-        <x:v>Capital expenditures</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="G25" s="26" t="n">
         <x:v>870000</x:v>
@@ -1440,7 +1440,7 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F31" s="23" t="str">
-        <x:v>Capital expenditures</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="G31" s="26" t="n">
         <x:v>620000</x:v>
@@ -1644,7 +1644,7 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F37" s="23" t="str">
-        <x:v>Capital expenditures</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="G37" s="26" t="n">
         <x:v>620000</x:v>
@@ -1848,7 +1848,7 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F43" s="23" t="str">
-        <x:v>Capital expenditures</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="G43" s="26" t="n">
         <x:v>620000</x:v>
@@ -2052,7 +2052,7 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F49" s="23" t="str">
-        <x:v>Capital expenditures</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="G49" s="26" t="n">
         <x:v>870000</x:v>
@@ -2240,38 +2240,548 @@
       <x:c r="L54" s="23" t="str"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="24" t="str">
+      <x:c r="A55" s="23" t="str">
         <x:v>048-SRC0053</x:v>
       </x:c>
-      <x:c r="B55" s="24" t="str">
+      <x:c r="B55" s="23" t="str">
         <x:v>Covenant policy</x:v>
       </x:c>
-      <x:c r="C55" s="24" t="str">
+      <x:c r="C55" s="23" t="str">
         <x:v>Credit agreement</x:v>
       </x:c>
-      <x:c r="D55" s="24" t="str">
+      <x:c r="D55" s="23" t="str">
         <x:v>Forecast horizon</x:v>
       </x:c>
-      <x:c r="E55" s="24" t="str">
-        <x:v>Approved case</x:v>
-      </x:c>
-      <x:c r="F55" s="24" t="str">
+      <x:c r="E55" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F55" s="23" t="str">
         <x:v>Minimum quarterly capex deduction</x:v>
       </x:c>
-      <x:c r="G55" s="27" t="n">
+      <x:c r="G55" s="26" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H55" s="24" t="str"/>
-      <x:c r="I55" s="24" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J55" s="24" t="str">
-        <x:v>Finance operating schedule</x:v>
-      </x:c>
-      <x:c r="K55" s="30" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L55" s="24" t="str"/>
+      <x:c r="H55" s="23" t="str"/>
+      <x:c r="I55" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J55" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K55" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L55" s="23" t="str"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="23" t="str">
+        <x:v>048-SRC0054</x:v>
+      </x:c>
+      <x:c r="B56" s="23" t="str">
+        <x:v>Historical Covenant Inputs</x:v>
+      </x:c>
+      <x:c r="C56" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D56" s="23" t="str">
+        <x:v>2025-Q4</x:v>
+      </x:c>
+      <x:c r="E56" s="23" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="F56" s="23" t="str">
+        <x:v>Quarterly covenant EBITDA</x:v>
+      </x:c>
+      <x:c r="G56" s="26" t="n">
+        <x:v>2850000</x:v>
+      </x:c>
+      <x:c r="H56" s="23" t="str"/>
+      <x:c r="I56" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J56" s="23" t="str">
+        <x:v>Q2 covenant history - controller tie</x:v>
+      </x:c>
+      <x:c r="K56" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L56" s="23" t="str"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="23" t="str">
+        <x:v>048-SRC0055</x:v>
+      </x:c>
+      <x:c r="B57" s="23" t="str">
+        <x:v>Historical Covenant Inputs</x:v>
+      </x:c>
+      <x:c r="C57" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D57" s="23" t="str">
+        <x:v>2025-Q4</x:v>
+      </x:c>
+      <x:c r="E57" s="23" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="F57" s="23" t="str">
+        <x:v>Cash interest</x:v>
+      </x:c>
+      <x:c r="G57" s="26" t="n">
+        <x:v>416000</x:v>
+      </x:c>
+      <x:c r="H57" s="23" t="str"/>
+      <x:c r="I57" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J57" s="23" t="str">
+        <x:v>Q2 covenant history - controller tie</x:v>
+      </x:c>
+      <x:c r="K57" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L57" s="23" t="str"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="23" t="str">
+        <x:v>048-SRC0056</x:v>
+      </x:c>
+      <x:c r="B58" s="23" t="str">
+        <x:v>Historical Covenant Inputs</x:v>
+      </x:c>
+      <x:c r="C58" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D58" s="23" t="str">
+        <x:v>2025-Q4</x:v>
+      </x:c>
+      <x:c r="E58" s="23" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="F58" s="23" t="str">
+        <x:v>Unfunded capital expenditures</x:v>
+      </x:c>
+      <x:c r="G58" s="26" t="n">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="H58" s="23" t="str"/>
+      <x:c r="I58" s="23" t="str">
+        <x:v>USD thousands</x:v>
+      </x:c>
+      <x:c r="J58" s="23" t="str">
+        <x:v>Q2 covenant history - controller tie</x:v>
+      </x:c>
+      <x:c r="K58" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L58" s="23" t="str"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="23" t="str">
+        <x:v>048-SRC0057</x:v>
+      </x:c>
+      <x:c r="B59" s="23" t="str">
+        <x:v>Historical Covenant Inputs</x:v>
+      </x:c>
+      <x:c r="C59" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D59" s="23" t="str">
+        <x:v>2025-Q4</x:v>
+      </x:c>
+      <x:c r="E59" s="23" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="F59" s="23" t="str">
+        <x:v>Cash taxes</x:v>
+      </x:c>
+      <x:c r="G59" s="26" t="n">
+        <x:v>280000</x:v>
+      </x:c>
+      <x:c r="H59" s="23" t="str"/>
+      <x:c r="I59" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J59" s="23" t="str">
+        <x:v>Q2 covenant history - controller tie</x:v>
+      </x:c>
+      <x:c r="K59" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L59" s="23" t="str"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="23" t="str">
+        <x:v>048-SRC0058</x:v>
+      </x:c>
+      <x:c r="B60" s="23" t="str">
+        <x:v>Historical Covenant Inputs</x:v>
+      </x:c>
+      <x:c r="C60" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D60" s="23" t="str">
+        <x:v>2025-Q4</x:v>
+      </x:c>
+      <x:c r="E60" s="23" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="F60" s="23" t="str">
+        <x:v>Scheduled debt repayment</x:v>
+      </x:c>
+      <x:c r="G60" s="26" t="n">
+        <x:v>650000</x:v>
+      </x:c>
+      <x:c r="H60" s="23" t="str"/>
+      <x:c r="I60" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J60" s="23" t="str">
+        <x:v>Q2 covenant history - controller tie</x:v>
+      </x:c>
+      <x:c r="K60" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L60" s="23" t="str"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="23" t="str">
+        <x:v>048-SRC0059</x:v>
+      </x:c>
+      <x:c r="B61" s="23" t="str">
+        <x:v>Historical Covenant Inputs</x:v>
+      </x:c>
+      <x:c r="C61" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D61" s="23" t="str">
+        <x:v>2026-Q1</x:v>
+      </x:c>
+      <x:c r="E61" s="23" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="F61" s="23" t="str">
+        <x:v>Quarterly covenant EBITDA</x:v>
+      </x:c>
+      <x:c r="G61" s="26" t="n">
+        <x:v>2920000</x:v>
+      </x:c>
+      <x:c r="H61" s="23" t="str"/>
+      <x:c r="I61" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J61" s="23" t="str">
+        <x:v>Q2 covenant history - controller tie</x:v>
+      </x:c>
+      <x:c r="K61" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L61" s="23" t="str"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="23" t="str">
+        <x:v>048-SRC0060</x:v>
+      </x:c>
+      <x:c r="B62" s="23" t="str">
+        <x:v>Historical Covenant Inputs</x:v>
+      </x:c>
+      <x:c r="C62" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D62" s="23" t="str">
+        <x:v>2026-Q1</x:v>
+      </x:c>
+      <x:c r="E62" s="23" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="F62" s="23" t="str">
+        <x:v>Cash interest</x:v>
+      </x:c>
+      <x:c r="G62" s="26" t="n">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="H62" s="23" t="str"/>
+      <x:c r="I62" s="23" t="str">
+        <x:v>USD thousands</x:v>
+      </x:c>
+      <x:c r="J62" s="23" t="str">
+        <x:v>Q2 covenant history - controller tie</x:v>
+      </x:c>
+      <x:c r="K62" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L62" s="23" t="str"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="23" t="str">
+        <x:v>048-SRC0061</x:v>
+      </x:c>
+      <x:c r="B63" s="23" t="str">
+        <x:v>Historical Covenant Inputs</x:v>
+      </x:c>
+      <x:c r="C63" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D63" s="23" t="str">
+        <x:v>2026-Q1</x:v>
+      </x:c>
+      <x:c r="E63" s="23" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="F63" s="23" t="str">
+        <x:v>Unfunded capital expenditures</x:v>
+      </x:c>
+      <x:c r="G63" s="26" t="n">
+        <x:v>610000</x:v>
+      </x:c>
+      <x:c r="H63" s="23" t="str"/>
+      <x:c r="I63" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J63" s="23" t="str">
+        <x:v>Q2 covenant history - controller tie</x:v>
+      </x:c>
+      <x:c r="K63" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L63" s="23" t="str"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="23" t="str">
+        <x:v>048-SRC0062</x:v>
+      </x:c>
+      <x:c r="B64" s="23" t="str">
+        <x:v>Historical Covenant Inputs</x:v>
+      </x:c>
+      <x:c r="C64" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D64" s="23" t="str">
+        <x:v>2026-Q1</x:v>
+      </x:c>
+      <x:c r="E64" s="23" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="F64" s="23" t="str">
+        <x:v>Cash taxes</x:v>
+      </x:c>
+      <x:c r="G64" s="26" t="n">
+        <x:v>290000</x:v>
+      </x:c>
+      <x:c r="H64" s="23" t="str"/>
+      <x:c r="I64" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J64" s="23" t="str">
+        <x:v>Q2 covenant history - controller tie</x:v>
+      </x:c>
+      <x:c r="K64" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L64" s="23" t="str"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="23" t="str">
+        <x:v>048-SRC0063</x:v>
+      </x:c>
+      <x:c r="B65" s="23" t="str">
+        <x:v>Historical Covenant Inputs</x:v>
+      </x:c>
+      <x:c r="C65" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D65" s="23" t="str">
+        <x:v>2026-Q1</x:v>
+      </x:c>
+      <x:c r="E65" s="23" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="F65" s="23" t="str">
+        <x:v>Scheduled debt repayment</x:v>
+      </x:c>
+      <x:c r="G65" s="26" t="n">
+        <x:v>650000</x:v>
+      </x:c>
+      <x:c r="H65" s="23" t="str"/>
+      <x:c r="I65" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J65" s="23" t="str">
+        <x:v>Q2 covenant history - controller tie</x:v>
+      </x:c>
+      <x:c r="K65" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L65" s="23" t="str"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="23" t="str">
+        <x:v>048-SRC0064</x:v>
+      </x:c>
+      <x:c r="B66" s="23" t="str">
+        <x:v>Historical Covenant Inputs</x:v>
+      </x:c>
+      <x:c r="C66" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D66" s="23" t="str">
+        <x:v>2026-Q2</x:v>
+      </x:c>
+      <x:c r="E66" s="23" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="F66" s="23" t="str">
+        <x:v>Quarterly covenant EBITDA</x:v>
+      </x:c>
+      <x:c r="G66" s="26" t="n">
+        <x:v>3010</x:v>
+      </x:c>
+      <x:c r="H66" s="23" t="str"/>
+      <x:c r="I66" s="23" t="str">
+        <x:v>USD thousands</x:v>
+      </x:c>
+      <x:c r="J66" s="23" t="str">
+        <x:v>Q2 covenant history - controller tie</x:v>
+      </x:c>
+      <x:c r="K66" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L66" s="23" t="str"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="23" t="str">
+        <x:v>048-SRC0065</x:v>
+      </x:c>
+      <x:c r="B67" s="23" t="str">
+        <x:v>Historical Covenant Inputs</x:v>
+      </x:c>
+      <x:c r="C67" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D67" s="23" t="str">
+        <x:v>2026-Q2</x:v>
+      </x:c>
+      <x:c r="E67" s="23" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="F67" s="23" t="str">
+        <x:v>Cash interest</x:v>
+      </x:c>
+      <x:c r="G67" s="26" t="n">
+        <x:v>452000</x:v>
+      </x:c>
+      <x:c r="H67" s="23" t="str"/>
+      <x:c r="I67" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J67" s="23" t="str">
+        <x:v>Q2 covenant history - controller tie</x:v>
+      </x:c>
+      <x:c r="K67" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L67" s="23" t="str"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="23" t="str">
+        <x:v>048-SRC0066</x:v>
+      </x:c>
+      <x:c r="B68" s="23" t="str">
+        <x:v>Historical Covenant Inputs</x:v>
+      </x:c>
+      <x:c r="C68" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D68" s="23" t="str">
+        <x:v>2026-Q2</x:v>
+      </x:c>
+      <x:c r="E68" s="23" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="F68" s="23" t="str">
+        <x:v>Unfunded capital expenditures</x:v>
+      </x:c>
+      <x:c r="G68" s="26" t="n">
+        <x:v>620000</x:v>
+      </x:c>
+      <x:c r="H68" s="23" t="str"/>
+      <x:c r="I68" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J68" s="23" t="str">
+        <x:v>Q2 covenant history - controller tie</x:v>
+      </x:c>
+      <x:c r="K68" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L68" s="23" t="str"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="23" t="str">
+        <x:v>048-SRC0067</x:v>
+      </x:c>
+      <x:c r="B69" s="23" t="str">
+        <x:v>Historical Covenant Inputs</x:v>
+      </x:c>
+      <x:c r="C69" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D69" s="23" t="str">
+        <x:v>2026-Q2</x:v>
+      </x:c>
+      <x:c r="E69" s="23" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="F69" s="23" t="str">
+        <x:v>Cash taxes</x:v>
+      </x:c>
+      <x:c r="G69" s="26" t="n">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="H69" s="23" t="str"/>
+      <x:c r="I69" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J69" s="23" t="str">
+        <x:v>Q2 covenant history - controller tie</x:v>
+      </x:c>
+      <x:c r="K69" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L69" s="23" t="str"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="24" t="str">
+        <x:v>048-SRC0068</x:v>
+      </x:c>
+      <x:c r="B70" s="24" t="str">
+        <x:v>Historical Covenant Inputs</x:v>
+      </x:c>
+      <x:c r="C70" s="24" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D70" s="24" t="str">
+        <x:v>2026-Q2</x:v>
+      </x:c>
+      <x:c r="E70" s="24" t="str">
+        <x:v>Actual</x:v>
+      </x:c>
+      <x:c r="F70" s="24" t="str">
+        <x:v>Scheduled debt repayment</x:v>
+      </x:c>
+      <x:c r="G70" s="27" t="n">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="H70" s="24" t="str"/>
+      <x:c r="I70" s="24" t="str">
+        <x:v>USD thousands</x:v>
+      </x:c>
+      <x:c r="J70" s="24" t="str">
+        <x:v>Q2 covenant history - controller tie</x:v>
+      </x:c>
+      <x:c r="K70" s="30" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L70" s="24" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>

--- a/companies/alder-ridge/source-files/Shared/Finance/Treasury/Bank - covenants/FY27 covenant forecast - WORKING.xlsx
+++ b/companies/alder-ridge/source-files/Shared/Finance/Treasury/Bank - covenants/FY27 covenant forecast - WORKING.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast Inputs" sheetId="1" r:id="Rb419116265204649"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="2" r:id="R4babc73c4be249e5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covenant Forecast" sheetId="3" r:id="R9ff1fcc6bc114be8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Downside" sheetId="4" r:id="R9cef0839a2d34a60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="5" r:id="R845b00f7c64142a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast Inputs" sheetId="1" r:id="Rd06b29ba1d474d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="2" r:id="R4d75fa889ba54f4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covenant Forecast" sheetId="3" r:id="R466b10b725504274"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Downside" sheetId="4" r:id="Re532705917a94a06"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="5" r:id="R17d04aa38d4345dc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -256,7 +256,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Alder Ridge Finance" id="{985C9149-0327-48D7-8FF3-3DEAF244E7DB}"/>
+  <xltc:person displayName="Alder Ridge Finance" id="{AC8FC73E-0160-4522-8806-D3B3F2009588}"/>
 </xltc:personList>
 </file>
 
@@ -471,7 +471,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the eight-quarter covenant forecast | Forecast Inputs</x:v>
+        <x:v>FY27 covenant outlook | Forecast Inputs</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -2240,548 +2240,38 @@
       <x:c r="L54" s="23" t="str"/>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" s="23" t="str">
+      <x:c r="A55" s="24" t="str">
         <x:v>048-SRC0053</x:v>
       </x:c>
-      <x:c r="B55" s="23" t="str">
+      <x:c r="B55" s="24" t="str">
         <x:v>Covenant policy</x:v>
       </x:c>
-      <x:c r="C55" s="23" t="str">
+      <x:c r="C55" s="24" t="str">
         <x:v>Credit agreement</x:v>
       </x:c>
-      <x:c r="D55" s="23" t="str">
+      <x:c r="D55" s="24" t="str">
         <x:v>Forecast horizon</x:v>
       </x:c>
-      <x:c r="E55" s="23" t="str">
-        <x:v>Approved case</x:v>
-      </x:c>
-      <x:c r="F55" s="23" t="str">
+      <x:c r="E55" s="24" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F55" s="24" t="str">
         <x:v>Minimum quarterly capex deduction</x:v>
       </x:c>
-      <x:c r="G55" s="26" t="n">
+      <x:c r="G55" s="27" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H55" s="23" t="str"/>
-      <x:c r="I55" s="23" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J55" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
-      </x:c>
-      <x:c r="K55" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L55" s="23" t="str"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="23" t="str">
-        <x:v>048-SRC0054</x:v>
-      </x:c>
-      <x:c r="B56" s="23" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
-      </x:c>
-      <x:c r="C56" s="23" t="str">
-        <x:v>Consolidated</x:v>
-      </x:c>
-      <x:c r="D56" s="23" t="str">
-        <x:v>2025-Q4</x:v>
-      </x:c>
-      <x:c r="E56" s="23" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="F56" s="23" t="str">
-        <x:v>Quarterly covenant EBITDA</x:v>
-      </x:c>
-      <x:c r="G56" s="26" t="n">
-        <x:v>2850000</x:v>
-      </x:c>
-      <x:c r="H56" s="23" t="str"/>
-      <x:c r="I56" s="23" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J56" s="23" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
-      </x:c>
-      <x:c r="K56" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L56" s="23" t="str"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="A57" s="23" t="str">
-        <x:v>048-SRC0055</x:v>
-      </x:c>
-      <x:c r="B57" s="23" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
-      </x:c>
-      <x:c r="C57" s="23" t="str">
-        <x:v>Consolidated</x:v>
-      </x:c>
-      <x:c r="D57" s="23" t="str">
-        <x:v>2025-Q4</x:v>
-      </x:c>
-      <x:c r="E57" s="23" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="F57" s="23" t="str">
-        <x:v>Cash interest</x:v>
-      </x:c>
-      <x:c r="G57" s="26" t="n">
-        <x:v>416000</x:v>
-      </x:c>
-      <x:c r="H57" s="23" t="str"/>
-      <x:c r="I57" s="23" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J57" s="23" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
-      </x:c>
-      <x:c r="K57" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L57" s="23" t="str"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="23" t="str">
-        <x:v>048-SRC0056</x:v>
-      </x:c>
-      <x:c r="B58" s="23" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
-      </x:c>
-      <x:c r="C58" s="23" t="str">
-        <x:v>Consolidated</x:v>
-      </x:c>
-      <x:c r="D58" s="23" t="str">
-        <x:v>2025-Q4</x:v>
-      </x:c>
-      <x:c r="E58" s="23" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="F58" s="23" t="str">
-        <x:v>Unfunded capital expenditures</x:v>
-      </x:c>
-      <x:c r="G58" s="26" t="n">
-        <x:v>600</x:v>
-      </x:c>
-      <x:c r="H58" s="23" t="str"/>
-      <x:c r="I58" s="23" t="str">
-        <x:v>USD thousands</x:v>
-      </x:c>
-      <x:c r="J58" s="23" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
-      </x:c>
-      <x:c r="K58" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L58" s="23" t="str"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="23" t="str">
-        <x:v>048-SRC0057</x:v>
-      </x:c>
-      <x:c r="B59" s="23" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
-      </x:c>
-      <x:c r="C59" s="23" t="str">
-        <x:v>Consolidated</x:v>
-      </x:c>
-      <x:c r="D59" s="23" t="str">
-        <x:v>2025-Q4</x:v>
-      </x:c>
-      <x:c r="E59" s="23" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="F59" s="23" t="str">
-        <x:v>Cash taxes</x:v>
-      </x:c>
-      <x:c r="G59" s="26" t="n">
-        <x:v>280000</x:v>
-      </x:c>
-      <x:c r="H59" s="23" t="str"/>
-      <x:c r="I59" s="23" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J59" s="23" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
-      </x:c>
-      <x:c r="K59" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L59" s="23" t="str"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="A60" s="23" t="str">
-        <x:v>048-SRC0058</x:v>
-      </x:c>
-      <x:c r="B60" s="23" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
-      </x:c>
-      <x:c r="C60" s="23" t="str">
-        <x:v>Consolidated</x:v>
-      </x:c>
-      <x:c r="D60" s="23" t="str">
-        <x:v>2025-Q4</x:v>
-      </x:c>
-      <x:c r="E60" s="23" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="F60" s="23" t="str">
-        <x:v>Scheduled debt repayment</x:v>
-      </x:c>
-      <x:c r="G60" s="26" t="n">
-        <x:v>650000</x:v>
-      </x:c>
-      <x:c r="H60" s="23" t="str"/>
-      <x:c r="I60" s="23" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J60" s="23" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
-      </x:c>
-      <x:c r="K60" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L60" s="23" t="str"/>
-    </x:row>
-    <x:row r="61">
-      <x:c r="A61" s="23" t="str">
-        <x:v>048-SRC0059</x:v>
-      </x:c>
-      <x:c r="B61" s="23" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
-      </x:c>
-      <x:c r="C61" s="23" t="str">
-        <x:v>Consolidated</x:v>
-      </x:c>
-      <x:c r="D61" s="23" t="str">
-        <x:v>2026-Q1</x:v>
-      </x:c>
-      <x:c r="E61" s="23" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="F61" s="23" t="str">
-        <x:v>Quarterly covenant EBITDA</x:v>
-      </x:c>
-      <x:c r="G61" s="26" t="n">
-        <x:v>2920000</x:v>
-      </x:c>
-      <x:c r="H61" s="23" t="str"/>
-      <x:c r="I61" s="23" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J61" s="23" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
-      </x:c>
-      <x:c r="K61" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L61" s="23" t="str"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="A62" s="23" t="str">
-        <x:v>048-SRC0060</x:v>
-      </x:c>
-      <x:c r="B62" s="23" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
-      </x:c>
-      <x:c r="C62" s="23" t="str">
-        <x:v>Consolidated</x:v>
-      </x:c>
-      <x:c r="D62" s="23" t="str">
-        <x:v>2026-Q1</x:v>
-      </x:c>
-      <x:c r="E62" s="23" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="F62" s="23" t="str">
-        <x:v>Cash interest</x:v>
-      </x:c>
-      <x:c r="G62" s="26" t="n">
-        <x:v>434</x:v>
-      </x:c>
-      <x:c r="H62" s="23" t="str"/>
-      <x:c r="I62" s="23" t="str">
-        <x:v>USD thousands</x:v>
-      </x:c>
-      <x:c r="J62" s="23" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
-      </x:c>
-      <x:c r="K62" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L62" s="23" t="str"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="A63" s="23" t="str">
-        <x:v>048-SRC0061</x:v>
-      </x:c>
-      <x:c r="B63" s="23" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
-      </x:c>
-      <x:c r="C63" s="23" t="str">
-        <x:v>Consolidated</x:v>
-      </x:c>
-      <x:c r="D63" s="23" t="str">
-        <x:v>2026-Q1</x:v>
-      </x:c>
-      <x:c r="E63" s="23" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="F63" s="23" t="str">
-        <x:v>Unfunded capital expenditures</x:v>
-      </x:c>
-      <x:c r="G63" s="26" t="n">
-        <x:v>610000</x:v>
-      </x:c>
-      <x:c r="H63" s="23" t="str"/>
-      <x:c r="I63" s="23" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J63" s="23" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
-      </x:c>
-      <x:c r="K63" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L63" s="23" t="str"/>
-    </x:row>
-    <x:row r="64">
-      <x:c r="A64" s="23" t="str">
-        <x:v>048-SRC0062</x:v>
-      </x:c>
-      <x:c r="B64" s="23" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
-      </x:c>
-      <x:c r="C64" s="23" t="str">
-        <x:v>Consolidated</x:v>
-      </x:c>
-      <x:c r="D64" s="23" t="str">
-        <x:v>2026-Q1</x:v>
-      </x:c>
-      <x:c r="E64" s="23" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="F64" s="23" t="str">
-        <x:v>Cash taxes</x:v>
-      </x:c>
-      <x:c r="G64" s="26" t="n">
-        <x:v>290000</x:v>
-      </x:c>
-      <x:c r="H64" s="23" t="str"/>
-      <x:c r="I64" s="23" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J64" s="23" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
-      </x:c>
-      <x:c r="K64" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L64" s="23" t="str"/>
-    </x:row>
-    <x:row r="65">
-      <x:c r="A65" s="23" t="str">
-        <x:v>048-SRC0063</x:v>
-      </x:c>
-      <x:c r="B65" s="23" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
-      </x:c>
-      <x:c r="C65" s="23" t="str">
-        <x:v>Consolidated</x:v>
-      </x:c>
-      <x:c r="D65" s="23" t="str">
-        <x:v>2026-Q1</x:v>
-      </x:c>
-      <x:c r="E65" s="23" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="F65" s="23" t="str">
-        <x:v>Scheduled debt repayment</x:v>
-      </x:c>
-      <x:c r="G65" s="26" t="n">
-        <x:v>650000</x:v>
-      </x:c>
-      <x:c r="H65" s="23" t="str"/>
-      <x:c r="I65" s="23" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J65" s="23" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
-      </x:c>
-      <x:c r="K65" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L65" s="23" t="str"/>
-    </x:row>
-    <x:row r="66">
-      <x:c r="A66" s="23" t="str">
-        <x:v>048-SRC0064</x:v>
-      </x:c>
-      <x:c r="B66" s="23" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
-      </x:c>
-      <x:c r="C66" s="23" t="str">
-        <x:v>Consolidated</x:v>
-      </x:c>
-      <x:c r="D66" s="23" t="str">
-        <x:v>2026-Q2</x:v>
-      </x:c>
-      <x:c r="E66" s="23" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="F66" s="23" t="str">
-        <x:v>Quarterly covenant EBITDA</x:v>
-      </x:c>
-      <x:c r="G66" s="26" t="n">
-        <x:v>3010</x:v>
-      </x:c>
-      <x:c r="H66" s="23" t="str"/>
-      <x:c r="I66" s="23" t="str">
-        <x:v>USD thousands</x:v>
-      </x:c>
-      <x:c r="J66" s="23" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
-      </x:c>
-      <x:c r="K66" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L66" s="23" t="str"/>
-    </x:row>
-    <x:row r="67">
-      <x:c r="A67" s="23" t="str">
-        <x:v>048-SRC0065</x:v>
-      </x:c>
-      <x:c r="B67" s="23" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
-      </x:c>
-      <x:c r="C67" s="23" t="str">
-        <x:v>Consolidated</x:v>
-      </x:c>
-      <x:c r="D67" s="23" t="str">
-        <x:v>2026-Q2</x:v>
-      </x:c>
-      <x:c r="E67" s="23" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="F67" s="23" t="str">
-        <x:v>Cash interest</x:v>
-      </x:c>
-      <x:c r="G67" s="26" t="n">
-        <x:v>452000</x:v>
-      </x:c>
-      <x:c r="H67" s="23" t="str"/>
-      <x:c r="I67" s="23" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J67" s="23" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
-      </x:c>
-      <x:c r="K67" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L67" s="23" t="str"/>
-    </x:row>
-    <x:row r="68">
-      <x:c r="A68" s="23" t="str">
-        <x:v>048-SRC0066</x:v>
-      </x:c>
-      <x:c r="B68" s="23" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
-      </x:c>
-      <x:c r="C68" s="23" t="str">
-        <x:v>Consolidated</x:v>
-      </x:c>
-      <x:c r="D68" s="23" t="str">
-        <x:v>2026-Q2</x:v>
-      </x:c>
-      <x:c r="E68" s="23" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="F68" s="23" t="str">
-        <x:v>Unfunded capital expenditures</x:v>
-      </x:c>
-      <x:c r="G68" s="26" t="n">
-        <x:v>620000</x:v>
-      </x:c>
-      <x:c r="H68" s="23" t="str"/>
-      <x:c r="I68" s="23" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J68" s="23" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
-      </x:c>
-      <x:c r="K68" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L68" s="23" t="str"/>
-    </x:row>
-    <x:row r="69">
-      <x:c r="A69" s="23" t="str">
-        <x:v>048-SRC0067</x:v>
-      </x:c>
-      <x:c r="B69" s="23" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
-      </x:c>
-      <x:c r="C69" s="23" t="str">
-        <x:v>Consolidated</x:v>
-      </x:c>
-      <x:c r="D69" s="23" t="str">
-        <x:v>2026-Q2</x:v>
-      </x:c>
-      <x:c r="E69" s="23" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="F69" s="23" t="str">
-        <x:v>Cash taxes</x:v>
-      </x:c>
-      <x:c r="G69" s="26" t="n">
-        <x:v>300000</x:v>
-      </x:c>
-      <x:c r="H69" s="23" t="str"/>
-      <x:c r="I69" s="23" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J69" s="23" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
-      </x:c>
-      <x:c r="K69" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L69" s="23" t="str"/>
-    </x:row>
-    <x:row r="70">
-      <x:c r="A70" s="24" t="str">
-        <x:v>048-SRC0068</x:v>
-      </x:c>
-      <x:c r="B70" s="24" t="str">
-        <x:v>Historical Covenant Inputs</x:v>
-      </x:c>
-      <x:c r="C70" s="24" t="str">
-        <x:v>Consolidated</x:v>
-      </x:c>
-      <x:c r="D70" s="24" t="str">
-        <x:v>2026-Q2</x:v>
-      </x:c>
-      <x:c r="E70" s="24" t="str">
-        <x:v>Actual</x:v>
-      </x:c>
-      <x:c r="F70" s="24" t="str">
-        <x:v>Scheduled debt repayment</x:v>
-      </x:c>
-      <x:c r="G70" s="27" t="n">
-        <x:v>650</x:v>
-      </x:c>
-      <x:c r="H70" s="24" t="str"/>
-      <x:c r="I70" s="24" t="str">
-        <x:v>USD thousands</x:v>
-      </x:c>
-      <x:c r="J70" s="24" t="str">
-        <x:v>Q2 covenant history - controller tie</x:v>
-      </x:c>
-      <x:c r="K70" s="30" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L70" s="24" t="str"/>
+      <x:c r="H55" s="24" t="str"/>
+      <x:c r="I55" s="24" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J55" s="24" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K55" s="30" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L55" s="24" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2812,7 +2302,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the eight-quarter covenant forecast | Debt Schedule</x:v>
+        <x:v>FY27 covenant outlook | Debt Schedule</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -2975,7 +2465,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the eight-quarter covenant forecast | Covenant Forecast</x:v>
+        <x:v>FY27 covenant outlook | Covenant Forecast</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -2987,7 +2477,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING TEMPLATE - complete with source-linked formulas; hardcoded headline results are not acceptable</x:v>
+        <x:v>WORKING MODEL • link calculations to supporting schedules and complete the control section</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -3200,7 +2690,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the eight-quarter covenant forecast | Downside</x:v>
+        <x:v>FY27 covenant outlook | Downside</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -3212,7 +2702,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING TEMPLATE - complete with source-linked formulas; hardcoded headline results are not acceptable</x:v>
+        <x:v>WORKING MODEL • link calculations to supporting schedules and complete the control section</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>
@@ -3232,25 +2722,25 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="32" t="str">
-        <x:v>first_covenant_breach</x:v>
+        <x:v>downside_first_covenant_breach</x:v>
       </x:c>
       <x:c r="B5" s="35"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33" t="str">
-        <x:v>required_debt_paydown</x:v>
+        <x:v>downside_required_debt_paydown</x:v>
       </x:c>
       <x:c r="B6" s="36"/>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="33" t="str">
-        <x:v>maximum_leverage</x:v>
+        <x:v>downside_maximum_leverage</x:v>
       </x:c>
       <x:c r="B7" s="36"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="34" t="str">
-        <x:v>minimum_fixed_charge_coverage</x:v>
+        <x:v>downside_minimum_fixed_charge_coverage</x:v>
       </x:c>
       <x:c r="B8" s="37"/>
     </x:row>
@@ -3424,7 +2914,7 @@
   <x:sheetData>
     <x:row r="1" ht="24" customHeight="1">
       <x:c r="A1" s="3" t="str">
-        <x:v>Complete the eight-quarter covenant forecast | Checks</x:v>
+        <x:v>FY27 covenant outlook | Checks</x:v>
       </x:c>
       <x:c r="B1" s="3"/>
       <x:c r="C1" s="3"/>
@@ -3436,7 +2926,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="6" t="str">
-        <x:v>WORKING TEMPLATE - complete with source-linked formulas; hardcoded headline results are not acceptable</x:v>
+        <x:v>WORKING MODEL • link calculations to supporting schedules and complete the control section</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="6"/>

--- a/companies/alder-ridge/source-files/Shared/Finance/Treasury/Bank - covenants/FY27 covenant forecast - WORKING.xlsx
+++ b/companies/alder-ridge/source-files/Shared/Finance/Treasury/Bank - covenants/FY27 covenant forecast - WORKING.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast Inputs" sheetId="1" r:id="Rd06b29ba1d474d4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="2" r:id="R4d75fa889ba54f4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covenant Forecast" sheetId="3" r:id="R466b10b725504274"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Downside" sheetId="4" r:id="Re532705917a94a06"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="5" r:id="R17d04aa38d4345dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Forecast Inputs" sheetId="1" r:id="Rd7e01c5ee28e4443"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt Schedule" sheetId="2" r:id="R804fc259ade14cdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Covenant Forecast" sheetId="3" r:id="Ra766a6b48f9045e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Downside" sheetId="4" r:id="R622d3c7a67044fb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Checks" sheetId="5" r:id="Rf106a3e8d3fc4225"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -256,7 +256,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <xltc:personList xmlns:xltc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <xltc:person displayName="Alder Ridge Finance" id="{AC8FC73E-0160-4522-8806-D3B3F2009588}"/>
+  <xltc:person displayName="Alder Ridge Finance" id="{4D4FD528-8704-4517-A03D-4EF315223417}"/>
 </xltc:personList>
 </file>
 
@@ -541,29 +541,29 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="22" t="str">
-        <x:v>048-SRC0003</x:v>
+        <x:v>048-SRC0002</x:v>
       </x:c>
       <x:c r="B5" s="22" t="str">
-        <x:v>Forecast Inputs</x:v>
+        <x:v>Opening Balances</x:v>
       </x:c>
       <x:c r="C5" s="22" t="str">
-        <x:v>Consolidated</x:v>
+        <x:v>Unrestricted cash</x:v>
       </x:c>
       <x:c r="D5" s="22" t="str">
-        <x:v>2026-Q3</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="E5" s="22" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F5" s="22" t="str">
-        <x:v>Quarterly covenant EBITDA</x:v>
+        <x:v>Posted unrestricted cash</x:v>
       </x:c>
       <x:c r="G5" s="25" t="n">
-        <x:v>3150000</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="H5" s="22" t="str"/>
       <x:c r="I5" s="22" t="str">
-        <x:v>USD</x:v>
+        <x:v>ledger allocation factor</x:v>
       </x:c>
       <x:c r="J5" s="22" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -571,36 +571,38 @@
       <x:c r="K5" s="28" t="str">
         <x:v>2026-06-30</x:v>
       </x:c>
-      <x:c r="L5" s="22" t="str"/>
+      <x:c r="L5" s="22" t="str">
+        <x:v>Vista ERP cash detail as of 2026-06-30; unrestricted company cash accounts</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="23" t="str">
-        <x:v>048-SRC0004</x:v>
+        <x:v>048-SRC0003</x:v>
       </x:c>
       <x:c r="B6" s="23" t="str">
-        <x:v>Forecast Inputs</x:v>
+        <x:v>Opening Balances</x:v>
       </x:c>
       <x:c r="C6" s="23" t="str">
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D6" s="23" t="str">
-        <x:v>2026-Q3</x:v>
+        <x:v>2026-06-30</x:v>
       </x:c>
       <x:c r="E6" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F6" s="23" t="str">
-        <x:v>Cash interest</x:v>
+        <x:v>Opening tangible net worth</x:v>
       </x:c>
       <x:c r="G6" s="26" t="n">
-        <x:v>470</x:v>
+        <x:v>3400000</x:v>
       </x:c>
       <x:c r="H6" s="23" t="str"/>
       <x:c r="I6" s="23" t="str">
-        <x:v>USD thousands</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="J6" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
+        <x:v>Q2 lender covenant workpaper, controller tie</x:v>
       </x:c>
       <x:c r="K6" s="29" t="str">
         <x:v>2026-06-30</x:v>
@@ -624,10 +626,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F7" s="23" t="str">
-        <x:v>Unfunded capital expenditures</x:v>
+        <x:v>Quarterly covenant EBITDA</x:v>
       </x:c>
       <x:c r="G7" s="26" t="n">
-        <x:v>620000</x:v>
+        <x:v>3150000</x:v>
       </x:c>
       <x:c r="H7" s="23" t="str"/>
       <x:c r="I7" s="23" t="str">
@@ -658,10 +660,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F8" s="23" t="str">
-        <x:v>Cash taxes</x:v>
+        <x:v>Cash interest</x:v>
       </x:c>
       <x:c r="G8" s="26" t="n">
-        <x:v>310000</x:v>
+        <x:v>470000</x:v>
       </x:c>
       <x:c r="H8" s="23" t="str"/>
       <x:c r="I8" s="23" t="str">
@@ -692,10 +694,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F9" s="23" t="str">
-        <x:v>Distributions</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="G9" s="26" t="n">
-        <x:v>100000</x:v>
+        <x:v>620000</x:v>
       </x:c>
       <x:c r="H9" s="23" t="str"/>
       <x:c r="I9" s="23" t="str">
@@ -726,10 +728,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F10" s="23" t="str">
-        <x:v>Scheduled debt repayment</x:v>
+        <x:v>Cash taxes</x:v>
       </x:c>
       <x:c r="G10" s="26" t="n">
-        <x:v>650</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="H10" s="23" t="str"/>
       <x:c r="I10" s="23" t="str">
@@ -754,16 +756,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D11" s="23" t="str">
-        <x:v>2026-Q4</x:v>
+        <x:v>2026-Q3</x:v>
       </x:c>
       <x:c r="E11" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F11" s="23" t="str">
-        <x:v>Quarterly covenant EBITDA</x:v>
+        <x:v>Distributions</x:v>
       </x:c>
       <x:c r="G11" s="26" t="n">
-        <x:v>3080000</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="H11" s="23" t="str"/>
       <x:c r="I11" s="23" t="str">
@@ -788,16 +790,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D12" s="23" t="str">
-        <x:v>2026-Q4</x:v>
+        <x:v>2026-Q3</x:v>
       </x:c>
       <x:c r="E12" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F12" s="23" t="str">
-        <x:v>Cash interest</x:v>
+        <x:v>Scheduled debt repayment</x:v>
       </x:c>
       <x:c r="G12" s="26" t="n">
-        <x:v>488000</x:v>
+        <x:v>650000</x:v>
       </x:c>
       <x:c r="H12" s="23" t="str"/>
       <x:c r="I12" s="23" t="str">
@@ -822,16 +824,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D13" s="23" t="str">
-        <x:v>2026-Q4</x:v>
+        <x:v>2026-Q3</x:v>
       </x:c>
       <x:c r="E13" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F13" s="23" t="str">
-        <x:v>Unfunded capital expenditures</x:v>
+        <x:v>Quarterly net income</x:v>
       </x:c>
       <x:c r="G13" s="26" t="n">
-        <x:v>620000</x:v>
+        <x:v>250000</x:v>
       </x:c>
       <x:c r="H13" s="23" t="str"/>
       <x:c r="I13" s="23" t="str">
@@ -856,16 +858,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D14" s="23" t="str">
-        <x:v>2026-Q4</x:v>
+        <x:v>2026-Q3</x:v>
       </x:c>
       <x:c r="E14" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F14" s="23" t="str">
-        <x:v>Cash taxes</x:v>
+        <x:v>Operating cash generation before interest, taxes, capex, distributions, and debt service</x:v>
       </x:c>
       <x:c r="G14" s="26" t="n">
-        <x:v>322</x:v>
+        <x:v>2250</x:v>
       </x:c>
       <x:c r="H14" s="23" t="str"/>
       <x:c r="I14" s="23" t="str">
@@ -896,10 +898,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F15" s="23" t="str">
-        <x:v>Distributions</x:v>
+        <x:v>Quarterly covenant EBITDA</x:v>
       </x:c>
       <x:c r="G15" s="26" t="n">
-        <x:v>100000</x:v>
+        <x:v>3080000</x:v>
       </x:c>
       <x:c r="H15" s="23" t="str"/>
       <x:c r="I15" s="23" t="str">
@@ -930,10 +932,10 @@
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F16" s="23" t="str">
-        <x:v>Scheduled debt repayment</x:v>
+        <x:v>Cash interest</x:v>
       </x:c>
       <x:c r="G16" s="26" t="n">
-        <x:v>650000</x:v>
+        <x:v>488000</x:v>
       </x:c>
       <x:c r="H16" s="23" t="str"/>
       <x:c r="I16" s="23" t="str">
@@ -958,16 +960,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D17" s="23" t="str">
-        <x:v>2027-Q1</x:v>
+        <x:v>2026-Q4</x:v>
       </x:c>
       <x:c r="E17" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F17" s="23" t="str">
-        <x:v>Quarterly covenant EBITDA</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="G17" s="26" t="n">
-        <x:v>3010000</x:v>
+        <x:v>620000</x:v>
       </x:c>
       <x:c r="H17" s="23" t="str"/>
       <x:c r="I17" s="23" t="str">
@@ -992,16 +994,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D18" s="23" t="str">
-        <x:v>2027-Q1</x:v>
+        <x:v>2026-Q4</x:v>
       </x:c>
       <x:c r="E18" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F18" s="23" t="str">
-        <x:v>Cash interest</x:v>
+        <x:v>Cash taxes</x:v>
       </x:c>
       <x:c r="G18" s="26" t="n">
-        <x:v>506</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="H18" s="23" t="str"/>
       <x:c r="I18" s="23" t="str">
@@ -1026,16 +1028,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D19" s="23" t="str">
-        <x:v>2027-Q1</x:v>
+        <x:v>2026-Q4</x:v>
       </x:c>
       <x:c r="E19" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F19" s="23" t="str">
-        <x:v>Unfunded capital expenditures</x:v>
+        <x:v>Distributions</x:v>
       </x:c>
       <x:c r="G19" s="26" t="n">
-        <x:v>620000</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="H19" s="23" t="str"/>
       <x:c r="I19" s="23" t="str">
@@ -1060,16 +1062,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D20" s="23" t="str">
-        <x:v>2027-Q1</x:v>
+        <x:v>2026-Q4</x:v>
       </x:c>
       <x:c r="E20" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F20" s="23" t="str">
-        <x:v>Cash taxes</x:v>
+        <x:v>Scheduled debt repayment</x:v>
       </x:c>
       <x:c r="G20" s="26" t="n">
-        <x:v>334000</x:v>
+        <x:v>650000</x:v>
       </x:c>
       <x:c r="H20" s="23" t="str"/>
       <x:c r="I20" s="23" t="str">
@@ -1094,16 +1096,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D21" s="23" t="str">
-        <x:v>2027-Q1</x:v>
+        <x:v>2026-Q4</x:v>
       </x:c>
       <x:c r="E21" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F21" s="23" t="str">
-        <x:v>Distributions</x:v>
+        <x:v>Quarterly net income</x:v>
       </x:c>
       <x:c r="G21" s="26" t="n">
-        <x:v>100000</x:v>
+        <x:v>225000</x:v>
       </x:c>
       <x:c r="H21" s="23" t="str"/>
       <x:c r="I21" s="23" t="str">
@@ -1128,16 +1130,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D22" s="23" t="str">
-        <x:v>2027-Q1</x:v>
+        <x:v>2026-Q4</x:v>
       </x:c>
       <x:c r="E22" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F22" s="23" t="str">
-        <x:v>Scheduled debt repayment</x:v>
+        <x:v>Operating cash generation before interest, taxes, capex, distributions, and debt service</x:v>
       </x:c>
       <x:c r="G22" s="26" t="n">
-        <x:v>650</x:v>
+        <x:v>1980</x:v>
       </x:c>
       <x:c r="H22" s="23" t="str"/>
       <x:c r="I22" s="23" t="str">
@@ -1162,7 +1164,7 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D23" s="23" t="str">
-        <x:v>2027-Q2</x:v>
+        <x:v>2027-Q1</x:v>
       </x:c>
       <x:c r="E23" s="23" t="str">
         <x:v>Approved case</x:v>
@@ -1171,7 +1173,7 @@
         <x:v>Quarterly covenant EBITDA</x:v>
       </x:c>
       <x:c r="G23" s="26" t="n">
-        <x:v>2940000</x:v>
+        <x:v>3010000</x:v>
       </x:c>
       <x:c r="H23" s="23" t="str"/>
       <x:c r="I23" s="23" t="str">
@@ -1196,7 +1198,7 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D24" s="23" t="str">
-        <x:v>2027-Q2</x:v>
+        <x:v>2027-Q1</x:v>
       </x:c>
       <x:c r="E24" s="23" t="str">
         <x:v>Approved case</x:v>
@@ -1205,7 +1207,7 @@
         <x:v>Cash interest</x:v>
       </x:c>
       <x:c r="G24" s="26" t="n">
-        <x:v>524000</x:v>
+        <x:v>506000</x:v>
       </x:c>
       <x:c r="H24" s="23" t="str"/>
       <x:c r="I24" s="23" t="str">
@@ -1230,7 +1232,7 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D25" s="23" t="str">
-        <x:v>2027-Q2</x:v>
+        <x:v>2027-Q1</x:v>
       </x:c>
       <x:c r="E25" s="23" t="str">
         <x:v>Approved case</x:v>
@@ -1239,7 +1241,7 @@
         <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="G25" s="26" t="n">
-        <x:v>870000</x:v>
+        <x:v>620000</x:v>
       </x:c>
       <x:c r="H25" s="23" t="str"/>
       <x:c r="I25" s="23" t="str">
@@ -1264,7 +1266,7 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D26" s="23" t="str">
-        <x:v>2027-Q2</x:v>
+        <x:v>2027-Q1</x:v>
       </x:c>
       <x:c r="E26" s="23" t="str">
         <x:v>Approved case</x:v>
@@ -1273,7 +1275,7 @@
         <x:v>Cash taxes</x:v>
       </x:c>
       <x:c r="G26" s="26" t="n">
-        <x:v>346</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="H26" s="23" t="str"/>
       <x:c r="I26" s="23" t="str">
@@ -1298,7 +1300,7 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D27" s="23" t="str">
-        <x:v>2027-Q2</x:v>
+        <x:v>2027-Q1</x:v>
       </x:c>
       <x:c r="E27" s="23" t="str">
         <x:v>Approved case</x:v>
@@ -1332,7 +1334,7 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D28" s="23" t="str">
-        <x:v>2027-Q2</x:v>
+        <x:v>2027-Q1</x:v>
       </x:c>
       <x:c r="E28" s="23" t="str">
         <x:v>Approved case</x:v>
@@ -1366,16 +1368,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D29" s="23" t="str">
-        <x:v>2027-Q3</x:v>
+        <x:v>2027-Q1</x:v>
       </x:c>
       <x:c r="E29" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F29" s="23" t="str">
-        <x:v>Quarterly covenant EBITDA</x:v>
+        <x:v>Quarterly net income</x:v>
       </x:c>
       <x:c r="G29" s="26" t="n">
-        <x:v>2870000</x:v>
+        <x:v>200000</x:v>
       </x:c>
       <x:c r="H29" s="23" t="str"/>
       <x:c r="I29" s="23" t="str">
@@ -1400,16 +1402,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D30" s="23" t="str">
-        <x:v>2027-Q3</x:v>
+        <x:v>2027-Q1</x:v>
       </x:c>
       <x:c r="E30" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F30" s="23" t="str">
-        <x:v>Cash interest</x:v>
+        <x:v>Operating cash generation before interest, taxes, capex, distributions, and debt service</x:v>
       </x:c>
       <x:c r="G30" s="26" t="n">
-        <x:v>542</x:v>
+        <x:v>2310</x:v>
       </x:c>
       <x:c r="H30" s="23" t="str"/>
       <x:c r="I30" s="23" t="str">
@@ -1434,16 +1436,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D31" s="23" t="str">
-        <x:v>2027-Q3</x:v>
+        <x:v>2027-Q2</x:v>
       </x:c>
       <x:c r="E31" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F31" s="23" t="str">
-        <x:v>Unfunded capital expenditures</x:v>
+        <x:v>Quarterly covenant EBITDA</x:v>
       </x:c>
       <x:c r="G31" s="26" t="n">
-        <x:v>620000</x:v>
+        <x:v>2940000</x:v>
       </x:c>
       <x:c r="H31" s="23" t="str"/>
       <x:c r="I31" s="23" t="str">
@@ -1468,16 +1470,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D32" s="23" t="str">
-        <x:v>2027-Q3</x:v>
+        <x:v>2027-Q2</x:v>
       </x:c>
       <x:c r="E32" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F32" s="23" t="str">
-        <x:v>Cash taxes</x:v>
+        <x:v>Cash interest</x:v>
       </x:c>
       <x:c r="G32" s="26" t="n">
-        <x:v>358000</x:v>
+        <x:v>524000</x:v>
       </x:c>
       <x:c r="H32" s="23" t="str"/>
       <x:c r="I32" s="23" t="str">
@@ -1502,16 +1504,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D33" s="23" t="str">
-        <x:v>2027-Q3</x:v>
+        <x:v>2027-Q2</x:v>
       </x:c>
       <x:c r="E33" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F33" s="23" t="str">
-        <x:v>Distributions</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="G33" s="26" t="n">
-        <x:v>100000</x:v>
+        <x:v>870000</x:v>
       </x:c>
       <x:c r="H33" s="23" t="str"/>
       <x:c r="I33" s="23" t="str">
@@ -1536,16 +1538,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D34" s="23" t="str">
-        <x:v>2027-Q3</x:v>
+        <x:v>2027-Q2</x:v>
       </x:c>
       <x:c r="E34" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F34" s="23" t="str">
-        <x:v>Scheduled debt repayment</x:v>
+        <x:v>Cash taxes</x:v>
       </x:c>
       <x:c r="G34" s="26" t="n">
-        <x:v>650</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="H34" s="23" t="str"/>
       <x:c r="I34" s="23" t="str">
@@ -1570,16 +1572,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D35" s="23" t="str">
-        <x:v>2027-Q4</x:v>
+        <x:v>2027-Q2</x:v>
       </x:c>
       <x:c r="E35" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F35" s="23" t="str">
-        <x:v>Quarterly covenant EBITDA</x:v>
+        <x:v>Distributions</x:v>
       </x:c>
       <x:c r="G35" s="26" t="n">
-        <x:v>2380000</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="H35" s="23" t="str"/>
       <x:c r="I35" s="23" t="str">
@@ -1604,16 +1606,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D36" s="23" t="str">
-        <x:v>2027-Q4</x:v>
+        <x:v>2027-Q2</x:v>
       </x:c>
       <x:c r="E36" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F36" s="23" t="str">
-        <x:v>Cash interest</x:v>
+        <x:v>Scheduled debt repayment</x:v>
       </x:c>
       <x:c r="G36" s="26" t="n">
-        <x:v>560000</x:v>
+        <x:v>650000</x:v>
       </x:c>
       <x:c r="H36" s="23" t="str"/>
       <x:c r="I36" s="23" t="str">
@@ -1638,16 +1640,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D37" s="23" t="str">
-        <x:v>2027-Q4</x:v>
+        <x:v>2027-Q2</x:v>
       </x:c>
       <x:c r="E37" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F37" s="23" t="str">
-        <x:v>Unfunded capital expenditures</x:v>
+        <x:v>Quarterly net income</x:v>
       </x:c>
       <x:c r="G37" s="26" t="n">
-        <x:v>620000</x:v>
+        <x:v>150000</x:v>
       </x:c>
       <x:c r="H37" s="23" t="str"/>
       <x:c r="I37" s="23" t="str">
@@ -1672,16 +1674,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D38" s="23" t="str">
-        <x:v>2027-Q4</x:v>
+        <x:v>2027-Q2</x:v>
       </x:c>
       <x:c r="E38" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F38" s="23" t="str">
-        <x:v>Cash taxes</x:v>
+        <x:v>Operating cash generation before interest, taxes, capex, distributions, and debt service</x:v>
       </x:c>
       <x:c r="G38" s="26" t="n">
-        <x:v>370</x:v>
+        <x:v>1440</x:v>
       </x:c>
       <x:c r="H38" s="23" t="str"/>
       <x:c r="I38" s="23" t="str">
@@ -1706,16 +1708,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D39" s="23" t="str">
-        <x:v>2027-Q4</x:v>
+        <x:v>2027-Q3</x:v>
       </x:c>
       <x:c r="E39" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F39" s="23" t="str">
-        <x:v>Distributions</x:v>
+        <x:v>Quarterly covenant EBITDA</x:v>
       </x:c>
       <x:c r="G39" s="26" t="n">
-        <x:v>100000</x:v>
+        <x:v>2870000</x:v>
       </x:c>
       <x:c r="H39" s="23" t="str"/>
       <x:c r="I39" s="23" t="str">
@@ -1740,16 +1742,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D40" s="23" t="str">
-        <x:v>2027-Q4</x:v>
+        <x:v>2027-Q3</x:v>
       </x:c>
       <x:c r="E40" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F40" s="23" t="str">
-        <x:v>Scheduled debt repayment</x:v>
+        <x:v>Cash interest</x:v>
       </x:c>
       <x:c r="G40" s="26" t="n">
-        <x:v>650000</x:v>
+        <x:v>542000</x:v>
       </x:c>
       <x:c r="H40" s="23" t="str"/>
       <x:c r="I40" s="23" t="str">
@@ -1774,16 +1776,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D41" s="23" t="str">
-        <x:v>2028-Q1</x:v>
+        <x:v>2027-Q3</x:v>
       </x:c>
       <x:c r="E41" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F41" s="23" t="str">
-        <x:v>Quarterly covenant EBITDA</x:v>
+        <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="G41" s="26" t="n">
-        <x:v>2310000</x:v>
+        <x:v>620000</x:v>
       </x:c>
       <x:c r="H41" s="23" t="str"/>
       <x:c r="I41" s="23" t="str">
@@ -1808,16 +1810,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D42" s="23" t="str">
-        <x:v>2028-Q1</x:v>
+        <x:v>2027-Q3</x:v>
       </x:c>
       <x:c r="E42" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F42" s="23" t="str">
-        <x:v>Cash interest</x:v>
+        <x:v>Cash taxes</x:v>
       </x:c>
       <x:c r="G42" s="26" t="n">
-        <x:v>578</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="H42" s="23" t="str"/>
       <x:c r="I42" s="23" t="str">
@@ -1842,16 +1844,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D43" s="23" t="str">
-        <x:v>2028-Q1</x:v>
+        <x:v>2027-Q3</x:v>
       </x:c>
       <x:c r="E43" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F43" s="23" t="str">
-        <x:v>Unfunded capital expenditures</x:v>
+        <x:v>Distributions</x:v>
       </x:c>
       <x:c r="G43" s="26" t="n">
-        <x:v>620000</x:v>
+        <x:v>100000</x:v>
       </x:c>
       <x:c r="H43" s="23" t="str"/>
       <x:c r="I43" s="23" t="str">
@@ -1876,16 +1878,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D44" s="23" t="str">
-        <x:v>2028-Q1</x:v>
+        <x:v>2027-Q3</x:v>
       </x:c>
       <x:c r="E44" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F44" s="23" t="str">
-        <x:v>Cash taxes</x:v>
+        <x:v>Scheduled debt repayment</x:v>
       </x:c>
       <x:c r="G44" s="26" t="n">
-        <x:v>382000</x:v>
+        <x:v>650000</x:v>
       </x:c>
       <x:c r="H44" s="23" t="str"/>
       <x:c r="I44" s="23" t="str">
@@ -1910,13 +1912,13 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D45" s="23" t="str">
-        <x:v>2028-Q1</x:v>
+        <x:v>2027-Q3</x:v>
       </x:c>
       <x:c r="E45" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F45" s="23" t="str">
-        <x:v>Distributions</x:v>
+        <x:v>Quarterly net income</x:v>
       </x:c>
       <x:c r="G45" s="26" t="n">
         <x:v>100000</x:v>
@@ -1944,16 +1946,16 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D46" s="23" t="str">
-        <x:v>2028-Q1</x:v>
+        <x:v>2027-Q3</x:v>
       </x:c>
       <x:c r="E46" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F46" s="23" t="str">
-        <x:v>Scheduled debt repayment</x:v>
+        <x:v>Operating cash generation before interest, taxes, capex, distributions, and debt service</x:v>
       </x:c>
       <x:c r="G46" s="26" t="n">
-        <x:v>650</x:v>
+        <x:v>2070</x:v>
       </x:c>
       <x:c r="H46" s="23" t="str"/>
       <x:c r="I46" s="23" t="str">
@@ -1978,7 +1980,7 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D47" s="23" t="str">
-        <x:v>2028-Q2</x:v>
+        <x:v>2027-Q4</x:v>
       </x:c>
       <x:c r="E47" s="23" t="str">
         <x:v>Approved case</x:v>
@@ -1987,7 +1989,7 @@
         <x:v>Quarterly covenant EBITDA</x:v>
       </x:c>
       <x:c r="G47" s="26" t="n">
-        <x:v>2240000</x:v>
+        <x:v>2380000</x:v>
       </x:c>
       <x:c r="H47" s="23" t="str"/>
       <x:c r="I47" s="23" t="str">
@@ -2012,7 +2014,7 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D48" s="23" t="str">
-        <x:v>2028-Q2</x:v>
+        <x:v>2027-Q4</x:v>
       </x:c>
       <x:c r="E48" s="23" t="str">
         <x:v>Approved case</x:v>
@@ -2021,7 +2023,7 @@
         <x:v>Cash interest</x:v>
       </x:c>
       <x:c r="G48" s="26" t="n">
-        <x:v>596000</x:v>
+        <x:v>560000</x:v>
       </x:c>
       <x:c r="H48" s="23" t="str"/>
       <x:c r="I48" s="23" t="str">
@@ -2046,7 +2048,7 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D49" s="23" t="str">
-        <x:v>2028-Q2</x:v>
+        <x:v>2027-Q4</x:v>
       </x:c>
       <x:c r="E49" s="23" t="str">
         <x:v>Approved case</x:v>
@@ -2055,7 +2057,7 @@
         <x:v>Unfunded capital expenditures</x:v>
       </x:c>
       <x:c r="G49" s="26" t="n">
-        <x:v>870000</x:v>
+        <x:v>620000</x:v>
       </x:c>
       <x:c r="H49" s="23" t="str"/>
       <x:c r="I49" s="23" t="str">
@@ -2080,7 +2082,7 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D50" s="23" t="str">
-        <x:v>2028-Q2</x:v>
+        <x:v>2027-Q4</x:v>
       </x:c>
       <x:c r="E50" s="23" t="str">
         <x:v>Approved case</x:v>
@@ -2089,7 +2091,7 @@
         <x:v>Cash taxes</x:v>
       </x:c>
       <x:c r="G50" s="26" t="n">
-        <x:v>394</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="H50" s="23" t="str"/>
       <x:c r="I50" s="23" t="str">
@@ -2114,7 +2116,7 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D51" s="23" t="str">
-        <x:v>2028-Q2</x:v>
+        <x:v>2027-Q4</x:v>
       </x:c>
       <x:c r="E51" s="23" t="str">
         <x:v>Approved case</x:v>
@@ -2148,7 +2150,7 @@
         <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D52" s="23" t="str">
-        <x:v>2028-Q2</x:v>
+        <x:v>2027-Q4</x:v>
       </x:c>
       <x:c r="E52" s="23" t="str">
         <x:v>Approved case</x:v>
@@ -2176,26 +2178,26 @@
         <x:v>048-SRC0051</x:v>
       </x:c>
       <x:c r="B53" s="23" t="str">
-        <x:v>Covenant policy</x:v>
+        <x:v>Forecast Inputs</x:v>
       </x:c>
       <x:c r="C53" s="23" t="str">
-        <x:v>Credit agreement</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D53" s="23" t="str">
-        <x:v>Forecast horizon</x:v>
+        <x:v>2027-Q4</x:v>
       </x:c>
       <x:c r="E53" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F53" s="23" t="str">
-        <x:v>Maximum funded-debt leverage</x:v>
+        <x:v>Quarterly net income</x:v>
       </x:c>
       <x:c r="G53" s="26" t="n">
-        <x:v>3.25</x:v>
+        <x:v>-100000</x:v>
       </x:c>
       <x:c r="H53" s="23" t="str"/>
       <x:c r="I53" s="23" t="str">
-        <x:v>multiple</x:v>
+        <x:v>USD</x:v>
       </x:c>
       <x:c r="J53" s="23" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -2210,68 +2212,782 @@
         <x:v>048-SRC0052</x:v>
       </x:c>
       <x:c r="B54" s="23" t="str">
-        <x:v>Covenant policy</x:v>
+        <x:v>Forecast Inputs</x:v>
       </x:c>
       <x:c r="C54" s="23" t="str">
-        <x:v>Credit agreement</x:v>
+        <x:v>Consolidated</x:v>
       </x:c>
       <x:c r="D54" s="23" t="str">
-        <x:v>Forecast horizon</x:v>
+        <x:v>2027-Q4</x:v>
       </x:c>
       <x:c r="E54" s="23" t="str">
         <x:v>Approved case</x:v>
       </x:c>
       <x:c r="F54" s="23" t="str">
-        <x:v>Minimum fixed-charge coverage</x:v>
+        <x:v>Operating cash generation before interest, taxes, capex, distributions, and debt service</x:v>
       </x:c>
       <x:c r="G54" s="26" t="n">
-        <x:v>1.2</x:v>
+        <x:v>1180</x:v>
       </x:c>
       <x:c r="H54" s="23" t="str"/>
       <x:c r="I54" s="23" t="str">
+        <x:v>USD thousands</x:v>
+      </x:c>
+      <x:c r="J54" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K54" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L54" s="23" t="str"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="23" t="str">
+        <x:v>048-SRC0053</x:v>
+      </x:c>
+      <x:c r="B55" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C55" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D55" s="23" t="str">
+        <x:v>2028-Q1</x:v>
+      </x:c>
+      <x:c r="E55" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F55" s="23" t="str">
+        <x:v>Quarterly covenant EBITDA</x:v>
+      </x:c>
+      <x:c r="G55" s="26" t="n">
+        <x:v>2310000</x:v>
+      </x:c>
+      <x:c r="H55" s="23" t="str"/>
+      <x:c r="I55" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J55" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K55" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L55" s="23" t="str"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="23" t="str">
+        <x:v>048-SRC0054</x:v>
+      </x:c>
+      <x:c r="B56" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C56" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D56" s="23" t="str">
+        <x:v>2028-Q1</x:v>
+      </x:c>
+      <x:c r="E56" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F56" s="23" t="str">
+        <x:v>Cash interest</x:v>
+      </x:c>
+      <x:c r="G56" s="26" t="n">
+        <x:v>578000</x:v>
+      </x:c>
+      <x:c r="H56" s="23" t="str"/>
+      <x:c r="I56" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J56" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K56" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L56" s="23" t="str"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="23" t="str">
+        <x:v>048-SRC0055</x:v>
+      </x:c>
+      <x:c r="B57" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C57" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D57" s="23" t="str">
+        <x:v>2028-Q1</x:v>
+      </x:c>
+      <x:c r="E57" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F57" s="23" t="str">
+        <x:v>Unfunded capital expenditures</x:v>
+      </x:c>
+      <x:c r="G57" s="26" t="n">
+        <x:v>620000</x:v>
+      </x:c>
+      <x:c r="H57" s="23" t="str"/>
+      <x:c r="I57" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J57" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K57" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L57" s="23" t="str"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="23" t="str">
+        <x:v>048-SRC0056</x:v>
+      </x:c>
+      <x:c r="B58" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C58" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D58" s="23" t="str">
+        <x:v>2028-Q1</x:v>
+      </x:c>
+      <x:c r="E58" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F58" s="23" t="str">
+        <x:v>Cash taxes</x:v>
+      </x:c>
+      <x:c r="G58" s="26" t="n">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="H58" s="23" t="str"/>
+      <x:c r="I58" s="23" t="str">
+        <x:v>USD thousands</x:v>
+      </x:c>
+      <x:c r="J58" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K58" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L58" s="23" t="str"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="23" t="str">
+        <x:v>048-SRC0057</x:v>
+      </x:c>
+      <x:c r="B59" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C59" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D59" s="23" t="str">
+        <x:v>2028-Q1</x:v>
+      </x:c>
+      <x:c r="E59" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F59" s="23" t="str">
+        <x:v>Distributions</x:v>
+      </x:c>
+      <x:c r="G59" s="26" t="n">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="H59" s="23" t="str"/>
+      <x:c r="I59" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J59" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K59" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L59" s="23" t="str"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="23" t="str">
+        <x:v>048-SRC0058</x:v>
+      </x:c>
+      <x:c r="B60" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C60" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D60" s="23" t="str">
+        <x:v>2028-Q1</x:v>
+      </x:c>
+      <x:c r="E60" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F60" s="23" t="str">
+        <x:v>Scheduled debt repayment</x:v>
+      </x:c>
+      <x:c r="G60" s="26" t="n">
+        <x:v>650000</x:v>
+      </x:c>
+      <x:c r="H60" s="23" t="str"/>
+      <x:c r="I60" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J60" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K60" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L60" s="23" t="str"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="23" t="str">
+        <x:v>048-SRC0059</x:v>
+      </x:c>
+      <x:c r="B61" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C61" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D61" s="23" t="str">
+        <x:v>2028-Q1</x:v>
+      </x:c>
+      <x:c r="E61" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F61" s="23" t="str">
+        <x:v>Quarterly net income</x:v>
+      </x:c>
+      <x:c r="G61" s="26" t="n">
+        <x:v>-200000</x:v>
+      </x:c>
+      <x:c r="H61" s="23" t="str"/>
+      <x:c r="I61" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J61" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K61" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L61" s="23" t="str"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="23" t="str">
+        <x:v>048-SRC0060</x:v>
+      </x:c>
+      <x:c r="B62" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C62" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D62" s="23" t="str">
+        <x:v>2028-Q1</x:v>
+      </x:c>
+      <x:c r="E62" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F62" s="23" t="str">
+        <x:v>Operating cash generation before interest, taxes, capex, distributions, and debt service</x:v>
+      </x:c>
+      <x:c r="G62" s="26" t="n">
+        <x:v>1460</x:v>
+      </x:c>
+      <x:c r="H62" s="23" t="str"/>
+      <x:c r="I62" s="23" t="str">
+        <x:v>USD thousands</x:v>
+      </x:c>
+      <x:c r="J62" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K62" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L62" s="23" t="str"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="23" t="str">
+        <x:v>048-SRC0061</x:v>
+      </x:c>
+      <x:c r="B63" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C63" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D63" s="23" t="str">
+        <x:v>2028-Q2</x:v>
+      </x:c>
+      <x:c r="E63" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F63" s="23" t="str">
+        <x:v>Quarterly covenant EBITDA</x:v>
+      </x:c>
+      <x:c r="G63" s="26" t="n">
+        <x:v>2240000</x:v>
+      </x:c>
+      <x:c r="H63" s="23" t="str"/>
+      <x:c r="I63" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J63" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K63" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L63" s="23" t="str"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="23" t="str">
+        <x:v>048-SRC0062</x:v>
+      </x:c>
+      <x:c r="B64" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C64" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D64" s="23" t="str">
+        <x:v>2028-Q2</x:v>
+      </x:c>
+      <x:c r="E64" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F64" s="23" t="str">
+        <x:v>Cash interest</x:v>
+      </x:c>
+      <x:c r="G64" s="26" t="n">
+        <x:v>596000</x:v>
+      </x:c>
+      <x:c r="H64" s="23" t="str"/>
+      <x:c r="I64" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J64" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K64" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L64" s="23" t="str"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="23" t="str">
+        <x:v>048-SRC0063</x:v>
+      </x:c>
+      <x:c r="B65" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C65" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D65" s="23" t="str">
+        <x:v>2028-Q2</x:v>
+      </x:c>
+      <x:c r="E65" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F65" s="23" t="str">
+        <x:v>Unfunded capital expenditures</x:v>
+      </x:c>
+      <x:c r="G65" s="26" t="n">
+        <x:v>870000</x:v>
+      </x:c>
+      <x:c r="H65" s="23" t="str"/>
+      <x:c r="I65" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J65" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K65" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L65" s="23" t="str"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="23" t="str">
+        <x:v>048-SRC0064</x:v>
+      </x:c>
+      <x:c r="B66" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C66" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D66" s="23" t="str">
+        <x:v>2028-Q2</x:v>
+      </x:c>
+      <x:c r="E66" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F66" s="23" t="str">
+        <x:v>Cash taxes</x:v>
+      </x:c>
+      <x:c r="G66" s="26" t="n">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="H66" s="23" t="str"/>
+      <x:c r="I66" s="23" t="str">
+        <x:v>USD thousands</x:v>
+      </x:c>
+      <x:c r="J66" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K66" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L66" s="23" t="str"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="23" t="str">
+        <x:v>048-SRC0065</x:v>
+      </x:c>
+      <x:c r="B67" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C67" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D67" s="23" t="str">
+        <x:v>2028-Q2</x:v>
+      </x:c>
+      <x:c r="E67" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F67" s="23" t="str">
+        <x:v>Distributions</x:v>
+      </x:c>
+      <x:c r="G67" s="26" t="n">
+        <x:v>100000</x:v>
+      </x:c>
+      <x:c r="H67" s="23" t="str"/>
+      <x:c r="I67" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J67" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K67" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L67" s="23" t="str"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="23" t="str">
+        <x:v>048-SRC0066</x:v>
+      </x:c>
+      <x:c r="B68" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C68" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D68" s="23" t="str">
+        <x:v>2028-Q2</x:v>
+      </x:c>
+      <x:c r="E68" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F68" s="23" t="str">
+        <x:v>Scheduled debt repayment</x:v>
+      </x:c>
+      <x:c r="G68" s="26" t="n">
+        <x:v>650000</x:v>
+      </x:c>
+      <x:c r="H68" s="23" t="str"/>
+      <x:c r="I68" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J68" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K68" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L68" s="23" t="str"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="23" t="str">
+        <x:v>048-SRC0067</x:v>
+      </x:c>
+      <x:c r="B69" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C69" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D69" s="23" t="str">
+        <x:v>2028-Q2</x:v>
+      </x:c>
+      <x:c r="E69" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F69" s="23" t="str">
+        <x:v>Quarterly net income</x:v>
+      </x:c>
+      <x:c r="G69" s="26" t="n">
+        <x:v>-250000</x:v>
+      </x:c>
+      <x:c r="H69" s="23" t="str"/>
+      <x:c r="I69" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J69" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K69" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L69" s="23" t="str"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="23" t="str">
+        <x:v>048-SRC0068</x:v>
+      </x:c>
+      <x:c r="B70" s="23" t="str">
+        <x:v>Forecast Inputs</x:v>
+      </x:c>
+      <x:c r="C70" s="23" t="str">
+        <x:v>Consolidated</x:v>
+      </x:c>
+      <x:c r="D70" s="23" t="str">
+        <x:v>2028-Q2</x:v>
+      </x:c>
+      <x:c r="E70" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F70" s="23" t="str">
+        <x:v>Operating cash generation before interest, taxes, capex, distributions, and debt service</x:v>
+      </x:c>
+      <x:c r="G70" s="26" t="n">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="H70" s="23" t="str"/>
+      <x:c r="I70" s="23" t="str">
+        <x:v>USD thousands</x:v>
+      </x:c>
+      <x:c r="J70" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K70" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L70" s="23" t="str"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="23" t="str">
+        <x:v>048-SRC0069</x:v>
+      </x:c>
+      <x:c r="B71" s="23" t="str">
+        <x:v>Covenant policy</x:v>
+      </x:c>
+      <x:c r="C71" s="23" t="str">
+        <x:v>Credit agreement</x:v>
+      </x:c>
+      <x:c r="D71" s="23" t="str">
+        <x:v>Forecast horizon</x:v>
+      </x:c>
+      <x:c r="E71" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F71" s="23" t="str">
+        <x:v>Maximum funded-debt leverage</x:v>
+      </x:c>
+      <x:c r="G71" s="26" t="n">
+        <x:v>3.25</x:v>
+      </x:c>
+      <x:c r="H71" s="23" t="str"/>
+      <x:c r="I71" s="23" t="str">
         <x:v>multiple</x:v>
       </x:c>
-      <x:c r="J54" s="23" t="str">
-        <x:v>Finance operating schedule</x:v>
-      </x:c>
-      <x:c r="K54" s="29" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L54" s="23" t="str"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="24" t="str">
-        <x:v>048-SRC0053</x:v>
-      </x:c>
-      <x:c r="B55" s="24" t="str">
+      <x:c r="J71" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K71" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L71" s="23" t="str"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="23" t="str">
+        <x:v>048-SRC0070</x:v>
+      </x:c>
+      <x:c r="B72" s="23" t="str">
         <x:v>Covenant policy</x:v>
       </x:c>
-      <x:c r="C55" s="24" t="str">
+      <x:c r="C72" s="23" t="str">
         <x:v>Credit agreement</x:v>
       </x:c>
-      <x:c r="D55" s="24" t="str">
+      <x:c r="D72" s="23" t="str">
         <x:v>Forecast horizon</x:v>
       </x:c>
-      <x:c r="E55" s="24" t="str">
-        <x:v>Approved case</x:v>
-      </x:c>
-      <x:c r="F55" s="24" t="str">
+      <x:c r="E72" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F72" s="23" t="str">
+        <x:v>Minimum fixed-charge coverage</x:v>
+      </x:c>
+      <x:c r="G72" s="26" t="n">
+        <x:v>1.2</x:v>
+      </x:c>
+      <x:c r="H72" s="23" t="str"/>
+      <x:c r="I72" s="23" t="str">
+        <x:v>multiple</x:v>
+      </x:c>
+      <x:c r="J72" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K72" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L72" s="23" t="str"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="23" t="str">
+        <x:v>048-SRC0071</x:v>
+      </x:c>
+      <x:c r="B73" s="23" t="str">
+        <x:v>Covenant policy</x:v>
+      </x:c>
+      <x:c r="C73" s="23" t="str">
+        <x:v>Credit agreement</x:v>
+      </x:c>
+      <x:c r="D73" s="23" t="str">
+        <x:v>Forecast horizon</x:v>
+      </x:c>
+      <x:c r="E73" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F73" s="23" t="str">
+        <x:v>Minimum tangible net worth</x:v>
+      </x:c>
+      <x:c r="G73" s="26" t="n">
+        <x:v>2500000</x:v>
+      </x:c>
+      <x:c r="H73" s="23" t="str"/>
+      <x:c r="I73" s="23" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J73" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K73" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L73" s="23" t="str"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="23" t="str">
+        <x:v>048-SRC0072</x:v>
+      </x:c>
+      <x:c r="B74" s="23" t="str">
+        <x:v>Covenant policy</x:v>
+      </x:c>
+      <x:c r="C74" s="23" t="str">
+        <x:v>Credit agreement</x:v>
+      </x:c>
+      <x:c r="D74" s="23" t="str">
+        <x:v>Forecast horizon</x:v>
+      </x:c>
+      <x:c r="E74" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F74" s="23" t="str">
+        <x:v>Board minimum unrestricted cash</x:v>
+      </x:c>
+      <x:c r="G74" s="26" t="n">
+        <x:v>2250</x:v>
+      </x:c>
+      <x:c r="H74" s="23" t="str"/>
+      <x:c r="I74" s="23" t="str">
+        <x:v>USD thousands</x:v>
+      </x:c>
+      <x:c r="J74" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K74" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L74" s="23" t="str"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="23" t="str">
+        <x:v>048-SRC0073</x:v>
+      </x:c>
+      <x:c r="B75" s="23" t="str">
+        <x:v>Covenant policy</x:v>
+      </x:c>
+      <x:c r="C75" s="23" t="str">
+        <x:v>Credit agreement</x:v>
+      </x:c>
+      <x:c r="D75" s="23" t="str">
+        <x:v>Forecast horizon</x:v>
+      </x:c>
+      <x:c r="E75" s="23" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F75" s="23" t="str">
+        <x:v>Downside net-income conversion tax rate</x:v>
+      </x:c>
+      <x:c r="G75" s="26" t="n">
+        <x:v>0.26</x:v>
+      </x:c>
+      <x:c r="H75" s="23" t="str"/>
+      <x:c r="I75" s="23" t="str">
+        <x:v>decimal ratio</x:v>
+      </x:c>
+      <x:c r="J75" s="23" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K75" s="29" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L75" s="23" t="str"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="24" t="str">
+        <x:v>048-SRC0074</x:v>
+      </x:c>
+      <x:c r="B76" s="24" t="str">
+        <x:v>Covenant policy</x:v>
+      </x:c>
+      <x:c r="C76" s="24" t="str">
+        <x:v>Credit agreement</x:v>
+      </x:c>
+      <x:c r="D76" s="24" t="str">
+        <x:v>Forecast horizon</x:v>
+      </x:c>
+      <x:c r="E76" s="24" t="str">
+        <x:v>Approved case</x:v>
+      </x:c>
+      <x:c r="F76" s="24" t="str">
         <x:v>Minimum quarterly capex deduction</x:v>
       </x:c>
-      <x:c r="G55" s="27" t="n">
+      <x:c r="G76" s="27" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H55" s="24" t="str"/>
-      <x:c r="I55" s="24" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="J55" s="24" t="str">
-        <x:v>Finance operating schedule</x:v>
-      </x:c>
-      <x:c r="K55" s="30" t="str">
-        <x:v>2026-06-30</x:v>
-      </x:c>
-      <x:c r="L55" s="24" t="str"/>
+      <x:c r="H76" s="24" t="str"/>
+      <x:c r="I76" s="24" t="str">
+        <x:v>USD</x:v>
+      </x:c>
+      <x:c r="J76" s="24" t="str">
+        <x:v>Finance operating schedule</x:v>
+      </x:c>
+      <x:c r="K76" s="30" t="str">
+        <x:v>2026-06-30</x:v>
+      </x:c>
+      <x:c r="L76" s="24" t="str"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2408,7 +3124,7 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="24" t="str">
-        <x:v>048-SRC0002</x:v>
+        <x:v>048-SRC0004</x:v>
       </x:c>
       <x:c r="B6" s="24" t="str">
         <x:v>Debt Schedule</x:v>
@@ -2426,11 +3142,11 @@
         <x:v>Committed draw</x:v>
       </x:c>
       <x:c r="G6" s="27" t="n">
-        <x:v>36000000</x:v>
+        <x:v>36000</x:v>
       </x:c>
       <x:c r="H6" s="24" t="str"/>
       <x:c r="I6" s="24" t="str">
-        <x:v>USD</x:v>
+        <x:v>USD thousands</x:v>
       </x:c>
       <x:c r="J6" s="24" t="str">
         <x:v>Finance operating schedule</x:v>
@@ -2514,106 +3230,82 @@
       <x:c r="B7" s="36"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="34" t="str">
+      <x:c r="A8" s="33" t="str">
         <x:v>minimum_fixed_charge_coverage</x:v>
       </x:c>
-      <x:c r="B8" s="37"/>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="15" t="str">
+      <x:c r="B8" s="36"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="33" t="str">
+        <x:v>first_liquidity_floor_breach</x:v>
+      </x:c>
+      <x:c r="B9" s="36"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="33" t="str">
+        <x:v>minimum_pre_financing_cash</x:v>
+      </x:c>
+      <x:c r="B10" s="36"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="33" t="str">
+        <x:v>cash_available_for_cure</x:v>
+      </x:c>
+      <x:c r="B11" s="36"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="33" t="str">
+        <x:v>cash_cure_funding_shortfall</x:v>
+      </x:c>
+      <x:c r="B12" s="36"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="33" t="str">
+        <x:v>first_tangible_net_worth_breach</x:v>
+      </x:c>
+      <x:c r="B13" s="36"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="34" t="str">
+        <x:v>minimum_tangible_net_worth</x:v>
+      </x:c>
+      <x:c r="B14" s="37"/>
+    </x:row>
+    <x:row r="17" ht="30" customHeight="1">
+      <x:c r="A17" s="15" t="str">
         <x:v>Period / Scenario</x:v>
       </x:c>
-      <x:c r="B11" s="16" t="str">
+      <x:c r="B17" s="16" t="str">
         <x:v>Business unit / item</x:v>
       </x:c>
-      <x:c r="C11" s="16" t="str">
+      <x:c r="C17" s="16" t="str">
         <x:v>Metric</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="str">
+      <x:c r="D17" s="16" t="str">
         <x:v>Input / driver</x:v>
       </x:c>
-      <x:c r="E11" s="16" t="str">
+      <x:c r="E17" s="16" t="str">
         <x:v>Formula output</x:v>
       </x:c>
-      <x:c r="F11" s="16" t="str">
+      <x:c r="F17" s="16" t="str">
         <x:v>Unit</x:v>
       </x:c>
-      <x:c r="G11" s="16" t="str">
+      <x:c r="G17" s="16" t="str">
         <x:v>Source / file / ref</x:v>
       </x:c>
-      <x:c r="H11" s="17" t="str">
+      <x:c r="H17" s="17" t="str">
         <x:v>Check</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="40"/>
-      <x:c r="B12" s="40"/>
-      <x:c r="C12" s="40"/>
-      <x:c r="D12" s="40"/>
-      <x:c r="E12" s="40"/>
-      <x:c r="F12" s="40"/>
-      <x:c r="G12" s="40"/>
-      <x:c r="H12" s="40"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="41"/>
-      <x:c r="B13" s="41"/>
-      <x:c r="C13" s="41"/>
-      <x:c r="D13" s="41"/>
-      <x:c r="E13" s="41"/>
-      <x:c r="F13" s="41"/>
-      <x:c r="G13" s="41"/>
-      <x:c r="H13" s="41"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="41"/>
-      <x:c r="B14" s="41"/>
-      <x:c r="C14" s="41"/>
-      <x:c r="D14" s="41"/>
-      <x:c r="E14" s="41"/>
-      <x:c r="F14" s="41"/>
-      <x:c r="G14" s="41"/>
-      <x:c r="H14" s="41"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="41"/>
-      <x:c r="B15" s="41"/>
-      <x:c r="C15" s="41"/>
-      <x:c r="D15" s="41"/>
-      <x:c r="E15" s="41"/>
-      <x:c r="F15" s="41"/>
-      <x:c r="G15" s="41"/>
-      <x:c r="H15" s="41"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="41"/>
-      <x:c r="B16" s="41"/>
-      <x:c r="C16" s="41"/>
-      <x:c r="D16" s="41"/>
-      <x:c r="E16" s="41"/>
-      <x:c r="F16" s="41"/>
-      <x:c r="G16" s="41"/>
-      <x:c r="H16" s="41"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="41"/>
-      <x:c r="B17" s="41"/>
-      <x:c r="C17" s="41"/>
-      <x:c r="D17" s="41"/>
-      <x:c r="E17" s="41"/>
-      <x:c r="F17" s="41"/>
-      <x:c r="G17" s="41"/>
-      <x:c r="H17" s="41"/>
-    </x:row>
     <x:row r="18">
-      <x:c r="A18" s="41"/>
-      <x:c r="B18" s="41"/>
-      <x:c r="C18" s="41"/>
-      <x:c r="D18" s="41"/>
-      <x:c r="E18" s="41"/>
-      <x:c r="F18" s="41"/>
-      <x:c r="G18" s="41"/>
-      <x:c r="H18" s="41"/>
+      <x:c r="A18" s="40"/>
+      <x:c r="B18" s="40"/>
+      <x:c r="C18" s="40"/>
+      <x:c r="D18" s="40"/>
+      <x:c r="E18" s="40"/>
+      <x:c r="F18" s="40"/>
+      <x:c r="G18" s="40"/>
+      <x:c r="H18" s="40"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="41"/>
@@ -2656,14 +3348,74 @@
       <x:c r="H22" s="41"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="42"/>
-      <x:c r="B23" s="42"/>
-      <x:c r="C23" s="42"/>
-      <x:c r="D23" s="42"/>
-      <x:c r="E23" s="42"/>
-      <x:c r="F23" s="42"/>
-      <x:c r="G23" s="42"/>
-      <x:c r="H23" s="42"/>
+      <x:c r="A23" s="41"/>
+      <x:c r="B23" s="41"/>
+      <x:c r="C23" s="41"/>
+      <x:c r="D23" s="41"/>
+      <x:c r="E23" s="41"/>
+      <x:c r="F23" s="41"/>
+      <x:c r="G23" s="41"/>
+      <x:c r="H23" s="41"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="41"/>
+      <x:c r="B24" s="41"/>
+      <x:c r="C24" s="41"/>
+      <x:c r="D24" s="41"/>
+      <x:c r="E24" s="41"/>
+      <x:c r="F24" s="41"/>
+      <x:c r="G24" s="41"/>
+      <x:c r="H24" s="41"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="41"/>
+      <x:c r="B25" s="41"/>
+      <x:c r="C25" s="41"/>
+      <x:c r="D25" s="41"/>
+      <x:c r="E25" s="41"/>
+      <x:c r="F25" s="41"/>
+      <x:c r="G25" s="41"/>
+      <x:c r="H25" s="41"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="41"/>
+      <x:c r="B26" s="41"/>
+      <x:c r="C26" s="41"/>
+      <x:c r="D26" s="41"/>
+      <x:c r="E26" s="41"/>
+      <x:c r="F26" s="41"/>
+      <x:c r="G26" s="41"/>
+      <x:c r="H26" s="41"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="41"/>
+      <x:c r="B27" s="41"/>
+      <x:c r="C27" s="41"/>
+      <x:c r="D27" s="41"/>
+      <x:c r="E27" s="41"/>
+      <x:c r="F27" s="41"/>
+      <x:c r="G27" s="41"/>
+      <x:c r="H27" s="41"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="41"/>
+      <x:c r="B28" s="41"/>
+      <x:c r="C28" s="41"/>
+      <x:c r="D28" s="41"/>
+      <x:c r="E28" s="41"/>
+      <x:c r="F28" s="41"/>
+      <x:c r="G28" s="41"/>
+      <x:c r="H28" s="41"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="42"/>
+      <x:c r="B29" s="42"/>
+      <x:c r="C29" s="42"/>
+      <x:c r="D29" s="42"/>
+      <x:c r="E29" s="42"/>
+      <x:c r="F29" s="42"/>
+      <x:c r="G29" s="42"/>
+      <x:c r="H29" s="42"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -2739,106 +3491,82 @@
       <x:c r="B7" s="36"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="34" t="str">
+      <x:c r="A8" s="33" t="str">
         <x:v>downside_minimum_fixed_charge_coverage</x:v>
       </x:c>
-      <x:c r="B8" s="37"/>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="15" t="str">
+      <x:c r="B8" s="36"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="33" t="str">
+        <x:v>downside_first_liquidity_floor_breach</x:v>
+      </x:c>
+      <x:c r="B9" s="36"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="33" t="str">
+        <x:v>downside_minimum_pre_financing_cash</x:v>
+      </x:c>
+      <x:c r="B10" s="36"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="33" t="str">
+        <x:v>downside_cash_available_for_cure</x:v>
+      </x:c>
+      <x:c r="B11" s="36"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="33" t="str">
+        <x:v>downside_cash_cure_funding_shortfall</x:v>
+      </x:c>
+      <x:c r="B12" s="36"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="33" t="str">
+        <x:v>downside_first_tangible_net_worth_breach</x:v>
+      </x:c>
+      <x:c r="B13" s="36"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="34" t="str">
+        <x:v>downside_minimum_tangible_net_worth</x:v>
+      </x:c>
+      <x:c r="B14" s="37"/>
+    </x:row>
+    <x:row r="17" ht="30" customHeight="1">
+      <x:c r="A17" s="15" t="str">
         <x:v>Period / Scenario</x:v>
       </x:c>
-      <x:c r="B11" s="16" t="str">
+      <x:c r="B17" s="16" t="str">
         <x:v>Business unit / item</x:v>
       </x:c>
-      <x:c r="C11" s="16" t="str">
+      <x:c r="C17" s="16" t="str">
         <x:v>Metric</x:v>
       </x:c>
-      <x:c r="D11" s="16" t="str">
+      <x:c r="D17" s="16" t="str">
         <x:v>Input / driver</x:v>
       </x:c>
-      <x:c r="E11" s="16" t="str">
+      <x:c r="E17" s="16" t="str">
         <x:v>Formula output</x:v>
       </x:c>
-      <x:c r="F11" s="16" t="str">
+      <x:c r="F17" s="16" t="str">
         <x:v>Unit</x:v>
       </x:c>
-      <x:c r="G11" s="16" t="str">
+      <x:c r="G17" s="16" t="str">
         <x:v>Source / file / ref</x:v>
       </x:c>
-      <x:c r="H11" s="17" t="str">
+      <x:c r="H17" s="17" t="str">
         <x:v>Check</x:v>
       </x:c>
     </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="40"/>
-      <x:c r="B12" s="40"/>
-      <x:c r="C12" s="40"/>
-      <x:c r="D12" s="40"/>
-      <x:c r="E12" s="40"/>
-      <x:c r="F12" s="40"/>
-      <x:c r="G12" s="40"/>
-      <x:c r="H12" s="40"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="41"/>
-      <x:c r="B13" s="41"/>
-      <x:c r="C13" s="41"/>
-      <x:c r="D13" s="41"/>
-      <x:c r="E13" s="41"/>
-      <x:c r="F13" s="41"/>
-      <x:c r="G13" s="41"/>
-      <x:c r="H13" s="41"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="41"/>
-      <x:c r="B14" s="41"/>
-      <x:c r="C14" s="41"/>
-      <x:c r="D14" s="41"/>
-      <x:c r="E14" s="41"/>
-      <x:c r="F14" s="41"/>
-      <x:c r="G14" s="41"/>
-      <x:c r="H14" s="41"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="41"/>
-      <x:c r="B15" s="41"/>
-      <x:c r="C15" s="41"/>
-      <x:c r="D15" s="41"/>
-      <x:c r="E15" s="41"/>
-      <x:c r="F15" s="41"/>
-      <x:c r="G15" s="41"/>
-      <x:c r="H15" s="41"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="41"/>
-      <x:c r="B16" s="41"/>
-      <x:c r="C16" s="41"/>
-      <x:c r="D16" s="41"/>
-      <x:c r="E16" s="41"/>
-      <x:c r="F16" s="41"/>
-      <x:c r="G16" s="41"/>
-      <x:c r="H16" s="41"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="41"/>
-      <x:c r="B17" s="41"/>
-      <x:c r="C17" s="41"/>
-      <x:c r="D17" s="41"/>
-      <x:c r="E17" s="41"/>
-      <x:c r="F17" s="41"/>
-      <x:c r="G17" s="41"/>
-      <x:c r="H17" s="41"/>
-    </x:row>
     <x:row r="18">
-      <x:c r="A18" s="41"/>
-      <x:c r="B18" s="41"/>
-      <x:c r="C18" s="41"/>
-      <x:c r="D18" s="41"/>
-      <x:c r="E18" s="41"/>
-      <x:c r="F18" s="41"/>
-      <x:c r="G18" s="41"/>
-      <x:c r="H18" s="41"/>
+      <x:c r="A18" s="40"/>
+      <x:c r="B18" s="40"/>
+      <x:c r="C18" s="40"/>
+      <x:c r="D18" s="40"/>
+      <x:c r="E18" s="40"/>
+      <x:c r="F18" s="40"/>
+      <x:c r="G18" s="40"/>
+      <x:c r="H18" s="40"/>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="41"/>
@@ -2881,14 +3609,74 @@
       <x:c r="H22" s="41"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="42"/>
-      <x:c r="B23" s="42"/>
-      <x:c r="C23" s="42"/>
-      <x:c r="D23" s="42"/>
-      <x:c r="E23" s="42"/>
-      <x:c r="F23" s="42"/>
-      <x:c r="G23" s="42"/>
-      <x:c r="H23" s="42"/>
+      <x:c r="A23" s="41"/>
+      <x:c r="B23" s="41"/>
+      <x:c r="C23" s="41"/>
+      <x:c r="D23" s="41"/>
+      <x:c r="E23" s="41"/>
+      <x:c r="F23" s="41"/>
+      <x:c r="G23" s="41"/>
+      <x:c r="H23" s="41"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="41"/>
+      <x:c r="B24" s="41"/>
+      <x:c r="C24" s="41"/>
+      <x:c r="D24" s="41"/>
+      <x:c r="E24" s="41"/>
+      <x:c r="F24" s="41"/>
+      <x:c r="G24" s="41"/>
+      <x:c r="H24" s="41"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="41"/>
+      <x:c r="B25" s="41"/>
+      <x:c r="C25" s="41"/>
+      <x:c r="D25" s="41"/>
+      <x:c r="E25" s="41"/>
+      <x:c r="F25" s="41"/>
+      <x:c r="G25" s="41"/>
+      <x:c r="H25" s="41"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="41"/>
+      <x:c r="B26" s="41"/>
+      <x:c r="C26" s="41"/>
+      <x:c r="D26" s="41"/>
+      <x:c r="E26" s="41"/>
+      <x:c r="F26" s="41"/>
+      <x:c r="G26" s="41"/>
+      <x:c r="H26" s="41"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="41"/>
+      <x:c r="B27" s="41"/>
+      <x:c r="C27" s="41"/>
+      <x:c r="D27" s="41"/>
+      <x:c r="E27" s="41"/>
+      <x:c r="F27" s="41"/>
+      <x:c r="G27" s="41"/>
+      <x:c r="H27" s="41"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="41"/>
+      <x:c r="B28" s="41"/>
+      <x:c r="C28" s="41"/>
+      <x:c r="D28" s="41"/>
+      <x:c r="E28" s="41"/>
+      <x:c r="F28" s="41"/>
+      <x:c r="G28" s="41"/>
+      <x:c r="H28" s="41"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="42"/>
+      <x:c r="B29" s="42"/>
+      <x:c r="C29" s="42"/>
+      <x:c r="D29" s="42"/>
+      <x:c r="E29" s="42"/>
+      <x:c r="F29" s="42"/>
+      <x:c r="G29" s="42"/>
+      <x:c r="H29" s="42"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
